--- a/Result/profitability/3086.xlsx
+++ b/Result/profitability/3086.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01499999999999999</v>
+        <v>0.006250000000000006</v>
       </c>
       <c r="N2" t="n">
-        <v>45.02125</v>
+        <v>41.6825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08250000000000002</v>
+        <v>0.07375000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>46.03</v>
+        <v>43.3025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03999999999999998</v>
+        <v>-0.07374999999999997</v>
       </c>
       <c r="N4" t="n">
-        <v>47.9</v>
+        <v>44.35249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09749999999999998</v>
+        <v>-0.01499999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>46.52374999999999</v>
+        <v>43.76625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.00249999999999998</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="N6" t="n">
-        <v>48.495</v>
+        <v>45.66249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00875000000000002</v>
+        <v>0.007500000000000029</v>
       </c>
       <c r="N7" t="n">
-        <v>50.05</v>
+        <v>47.29375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02625000000000002</v>
+        <v>0.02125000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>51.285</v>
+        <v>49.69875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.03</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03125000000000002</v>
+        <v>0.03125000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>54.64375</v>
@@ -1645,7 +1645,7 @@
         <v>0.34</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01749999999999997</v>
+        <v>-0.01749999999999996</v>
       </c>
       <c r="N10" t="n">
         <v>56.36125</v>
@@ -1772,10 +1772,10 @@
         <v>0.51</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02374999999999998</v>
+        <v>-0.02374999999999997</v>
       </c>
       <c r="N11" t="n">
-        <v>57.83500000000001</v>
+        <v>57.83499999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3086</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>37</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-39.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.56625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.69</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3656006914433881</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9295774647887324</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5004537205081669</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
